--- a/data/ll_content_review.xlsx
+++ b/data/ll_content_review.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\living-lab-explorer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E465B6D1-7BEC-4E7F-9B0C-9A0557AD1B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1E39C1B-8628-4869-8E12-359A76C8B5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="East Brandenburg" sheetId="2" r:id="rId1"/>
     <sheet name="Havelländisches Luch" sheetId="3" r:id="rId2"/>
-    <sheet name="North Hessian Loess Plain" sheetId="4" r:id="rId3"/>
+    <sheet name="North Hessian " sheetId="4" r:id="rId3"/>
     <sheet name="Hessian Low Mountain Range" sheetId="5" r:id="rId4"/>
     <sheet name="Rheingau" sheetId="6" r:id="rId5"/>
   </sheets>
@@ -23,8 +23,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={19299B7F-6951-4032-995A-F4A142CB96AA}</author>
+  </authors>
+  <commentList>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{19299B7F-6951-4032-995A-F4A142CB96AA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    google map entry is outdated, tehy recently moved with their office: https://share.google/xhoVIP4xxF6lyL6bZ</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="174">
   <si>
     <t>Field</t>
   </si>
@@ -41,9 +59,6 @@
     <t>Climate</t>
   </si>
   <si>
-    <t>East Brandenburg / Ost-Brandenburg</t>
-  </si>
-  <si>
     <t>Manager: Julia Gunnoltz &lt;Julia.Gunnoltz@zalf.de&gt;   |   Slug: east-brandenburg</t>
   </si>
   <si>
@@ -62,27 +77,18 @@
     <t>Lowland region shaped by multiple ice age glaciations. Minimal elevation differences with predominantly flat terrain with Oderbruch as a wide river valley shaped by glacial meltwater</t>
   </si>
   <si>
-    <t>Dominated by sandy and loamy-sandy soils ('Märkischer Sand') with low natural fertility. Müncheberger Soil Rating: Mostly very low to low soil quality (below 50 points); medium-quality soils only in specific floodplain regions (e.g., Oderbruch). High spatial heterogeneity of soil quality within single fields due to glacial landscape formation</t>
-  </si>
-  <si>
     <t>EN — Challenges</t>
   </si>
   <si>
     <t>Greater irrigation demand and competition for scarce water resources. Reduced crop productivity and stability under intensifying climate stress. High adaptation pressure on farmers, requiring new practices and investments. Competition for land between agriculture and renewable energy expansion. Decline in livestock diversity (pigs, cattle, sheep, goats). Limited horticulture and specialized crop production (low diversification). Balancing organic and conventional farming practices while maintaining productivity.</t>
   </si>
   <si>
-    <t>High drought vulnerability due to limited soil water retention capability</t>
-  </si>
-  <si>
     <t>Agriculture and peripheral industries generate limited regional value creation. Weak local processing and value-adding facilities limits regional economic integration, many areas faced a decline of traditional manufacturing and industrial sites. Skilled labor shortage (Fachkräftemangel) compounded by competition with Berlin’s dynamic job market</t>
   </si>
   <si>
     <t>Biodiversity decline in agricultural landscapes (e.g., drying of breeding habitats for amphibians). Land ownership: much farmland not owned by farmers.</t>
   </si>
   <si>
-    <t>⚠ NEEDS INPUT</t>
-  </si>
-  <si>
     <t>Hauptanbauprodukte: Wintergetreide, Mais für Silage/Energie, Winterraps; sonstige Landnutzung: Gartenbau sowie Saatgut- und Pflanzenanbau in geringem Umfang; Dauergrünland. Tierhaltung: Geflügel ist am weitesten verbreitet; Schweine, Rinder, Schafe und Ziegen sind rückläufig.</t>
   </si>
   <si>
@@ -95,27 +101,18 @@
     <t>Eine durch mehrere Vergletscherungen der Eiszeit geprägte Tieflandregion. Geringe Höhenunterschiede mit überwiegend flachem Gelände, wobei der Oderbruch ein breites, durch Gletscherschmelzwasser geformtes Flusstal darstellt.</t>
   </si>
   <si>
-    <t>Es überwiegen sandige und lehmig-sandige Böden („Märkischer Sand“) mit geringer natürlicher Fruchtbarkeit. Müncheberger Bodenbewertung: Überwiegend sehr geringe bis geringe Bodenqualität (unter 50 Punkten); Böden mittlerer Qualität nur in bestimmten Auengebieten (z. B. im Oderbruch). Hohe räumliche Heterogenität der Bodenqualität innerhalb einzelner Felder aufgrund der glazialen Landschaftsbildung</t>
-  </si>
-  <si>
     <t>DE — Challenges</t>
   </si>
   <si>
     <t>Steigender Bewässerungsbedarf und Wettbewerb um knappe Wasserressourcen. Geringere Ernteerträge und geringere Ertragssicherheit angesichts zunehmender klimatischer Belastungen. Hoher Anpassungsdruck auf die Landwirte, der neue Anbaumethoden und Investitionen erfordert. Wettbewerb um Flächen zwischen der Landwirtschaft und dem Ausbau erneuerbarer Energien. Rückgang der Vielfalt im Viehbestand (Schweine, Rinder, Schafe, Ziegen). Begrenzte Gartenbau- und Spezialkulturanbauaktivitäten (geringe Diversifizierung). Ausgewogenes Verhältnis zwischen ökologischen und konventionellen Anbaumethoden bei gleichbleibender Produktivität.</t>
   </si>
   <si>
-    <t>Hohe Anfälligkeit für Dürre aufgrund der begrenzten Wasserrückhaltefähigkeit des Bodens.</t>
-  </si>
-  <si>
     <t>Die Landwirtschaft und die damit verbundenen Branchen tragen nur in begrenztem Umfang zur regionalen Wertschöpfung bei. Die schwachen lokalen Verarbeitungs- und Wertschöpfungsstrukturen schränken die regionale wirtschaftliche Integration ein, und viele Gebiete waren mit einem Rückgang traditioneller Produktions- und Industriestandorte konfrontiert. Der Fachkräftemangel wird durch die Konkurrenz mit dem dynamischen Arbeitsmarkt Berlins noch verschärft.</t>
   </si>
   <si>
     <t>Rückgang der Artenvielfalt in Agrarlandschaften (z. B. Austrocknung von Laichhabitaten für Amphibien). Landbesitz: Ein Großteil der landwirtschaftlichen Flächen befindet sich nicht im Besitz der Landwirte.</t>
   </si>
   <si>
-    <t>Havelländisches Luch / Havelländisches Luch</t>
-  </si>
-  <si>
     <t>Manager: Sebastian Rogga &lt;Sebastian.Rogga@zalf.de&gt;   |   Slug: havellandisches-luch</t>
   </si>
   <si>
@@ -128,15 +125,9 @@
     <t>The socio-economic situation of the Havelland region is strongly influenced by its proximity to Berlin, with the eastern part of the region, which is close to the city, differing significantly from the rural western part. The population and building density is much higher in the east. The towns of Falkensee and Nauen, which are close to Berlin, have grown rapidly in recent years, and the district is among the top 15 in Germany in terms of positive net migration. Most industrial companies (especially in the logistics sector) are also located in the east of the district. The importance of tourism (especially water tourism) has increased recently. The unemployment rate is relatively low compared to the rest of the state. However, household incomes are among the lowest in Germany.</t>
   </si>
   <si>
-    <t>Havelland is classified as part of the North German inland lowlands and has sandy, diluvial soils. The quality of the arable soil increases from west to east.</t>
-  </si>
-  <si>
     <t>Agriculture in the Havelland district is characterised by location and land conditions (wetlands, predominance of grassland, varying soil quality) and is simultaneously subject to growing external demands (animal welfare, biodiversity, environmental protection, economic efficiency, climate change, and in the east of the region: land use pressure from competing land users). The combination of different uses (arable land, grassland, animal husbandry) and coordination with water/soil/nature conservation associations make the situation complex. Water management requirements clash with outdated water regulation technology.</t>
   </si>
   <si>
-    <t>Due to increasing evaporation, the climatic water balance in the area under consideration is generally deteriorating. This is particularly evident in summer and is a development that will become increasingly significant in the future.</t>
-  </si>
-  <si>
     <t>Landwirtschaft und Viehzucht prägen weite Teile des Havellands. Über 80 % der landwirtschaftlichen Nutzfläche werden von Betrieben bewirtschaftet, die jeweils mehr als 100 ha Ackerland besitzen. Kleinbetriebe machen lediglich 3,6 % der Fläche aus. Aufgrund des hohen Grünlandanteils in der Region sind Rinder-, Pferde- und Schafzucht von besonderer Bedeutung. Es wird eine große Vielfalt an Kulturpflanzen angebaut, von Roggen und Gerste bis hin zu Mais, Kartoffeln, hochwertigem Weizen und Rüben. Teile der Havelländischen Luch sind aufgrund ihrer Nähe zum Grundwasser zudem für den Ackerbau attraktiv.</t>
   </si>
   <si>
@@ -146,21 +137,9 @@
     <t>Die sozioökonomische Lage der Region Havelland wird stark durch ihre Nähe zu Berlin geprägt, wobei sich der östliche Teil der Region, der in der Nähe der Hauptstadt liegt, deutlich vom ländlichen westlichen Teil unterscheidet. Die Bevölkerungs- und Bebauungsdichte ist im Osten wesentlich höher. Die Städte Falkensee und Nauen, die in der Nähe von Berlin liegen, sind in den letzten Jahren rasant gewachsen, und der Landkreis gehört hinsichtlich der positiven Wanderungsbilanz zu den 15 führenden in Deutschland. Auch die meisten Industrieunternehmen (insbesondere im Logistiksektor) sind im Osten des Kreises angesiedelt. Die Bedeutung des Tourismus (insbesondere des Wassertourismus) hat in letzter Zeit zugenommen. Die Arbeitslosenquote ist im Vergleich zum Rest des Landes relativ niedrig. Die Haushaltseinkommen gehören jedoch zu den niedrigsten in Deutschland.</t>
   </si>
   <si>
-    <t>Havelland gehört zur norddeutschen Tiefebene und verfügt über sandige Schwemmlandböden. Die Qualität der Ackerböden nimmt von Westen nach Osten zu.</t>
-  </si>
-  <si>
     <t>Die Landwirtschaft im Landkreis Havelland ist durch die Lage und die Bodenverhältnisse (Feuchtgebiete, überwiegender Grünlandanteil, unterschiedliche Bodenqualität) geprägt und unterliegt gleichzeitig wachsenden externen Anforderungen (Tierschutz, Biodiversität, Umweltschutz, Wirtschaftlichkeit, Klimawandel sowie im Osten der Region: Flächennutzungsdruck durch konkurrierende Landnutzer). Die Kombination verschiedener Nutzungsformen (Ackerland, Grünland, Tierhaltung) und die Abstimmung mit Wasser-, Boden- und Naturschutzverbänden machen die Situation komplex. Anforderungen an die Wasserwirtschaft stehen im Widerspruch zu veralteter Wasserregulierungstechnik.</t>
   </si>
   <si>
-    <t>Aufgrund der zunehmenden Verdunstung verschlechtert sich der klimatische Wasserhaushalt im betrachteten Gebiet insgesamt. Dies macht sich insbesondere im Sommer bemerkbar und ist eine Entwicklung, die in Zukunft zunehmend an Bedeutung gewinnen wird.</t>
-  </si>
-  <si>
-    <t>North Hessian Loess Plain / Nordhessische Lössebene</t>
-  </si>
-  <si>
-    <t>Manager: Silke Flörke &lt;Silke.Floerke@zalf.de&gt;   |   Slug: north-hessian-loess</t>
-  </si>
-  <si>
     <t>Farming is small-structured and cereal-dominated: winter wheat, winter barley and winter rape form the backbone of the rotation, with cereals on around two thirds of the arable area, alongside fodder cropping, oilseeds and a widening range of niche crops — the Werra-Meißner-Kreis is Hesse's leading hemp-growing district. Organic farming is unusually strong and nearly doubled between 2009 and 2019, reaching 12% of farms and 14.4% of the agricultural area in the Werra-Meißner-Kreis, well above the national level; it is anchored by the University of Kassel's Faculty of Organic Agricultural Sciences in Witzenhausen — the first of its kind worldwide — the state domain Frankenhausen and the Ökolandbau-Modellregion Nordhessen. Livestock density is comparatively low and falling, with dairy in sharp retreat while suckler cows, sheep, horses and poultry gain ground. Roughly a third of the arable land and more than half of the grassland is under agri-environment contracts or organic management.</t>
   </si>
   <si>
@@ -191,9 +170,6 @@
     <t>The loess soils have been cultivated for centuries and are already truncated by erosion; on undulating terrain heavy rain moves soil off the slopes, which is why erosion-control and buffer strips are a standing element of the agri-environment programme. Outside the loess basins yield potential is low, and the shallow soils store little water, so they are the first to suffer in dry years. Cereal-dominated rotations depress humus content, while the region's low livestock density means little farmyard manure is available to rebuild it.</t>
   </si>
   <si>
-    <t>Die Landwirtschaft ist kleinstrukturiert und getreidebetont: Winterweizen, Wintergerste und Winterraps bilden das Grundgerüst der Fruchtfolge, Getreide steht auf rund zwei Dritteln der Ackerfläche, daneben Feldfutterbau, Ölfrüchte und ein wachsendes Spektrum an Nischenkulturen – beim Hanfanbau ist der Werra-Meißner-Kreis hessenweit führend. Der Ökolandbau ist ungewöhnlich stark und hat sich zwischen 2009 und 2019 nahezu verdoppelt: Im Werra-Meißner-Kreis wirtschaften 12 % der Betriebe auf 14,4 % der landwirtschaftlichen Nutzfläche ökologisch, deutlich über dem Bundeswert; getragen wird dies vom Fachbereich Ökologische Agrarwissenschaften der Universität Kassel in Witzenhausen – dem weltweit ersten seiner Art –, der Staatsdomäne Frankenhausen und der Ökolandbau-Modellregion Nordhessen. Die Nutztierdichte ist vergleichsweise gering und rückläufig: Die Milchviehhaltung geht stark zurück, während Mutterkühe, Schafe, Pferde und Geflügel zulegen. Rund ein Drittel der Ackerflächen und über die Hälfte des Grünlands werden über Agrarumweltmaßnahmen oder ökologisch bewirtschaftet.</t>
-  </si>
-  <si>
     <t>Die Becken liegen im Regenschatten der umgebenden Mittelgebirge und sind ausgesprochen trocken: 500–600 mm Jahresniederschlag im Kasseler Becken und in den Lössbörden stehen 800–900 mm auf den Höhen von Habichtswald, Kaufunger Wald und Meißner gegenüber. Die Jahresmitteltemperatur liegt in den Beckenlagen bei knapp 9,5 °C und in den Höhenlagen deutlich darunter, wo die Vegetationsperiode später beginnt. Die Jahresmitteltemperatur in Hessen stieg von 8,2 °C (1961–1990) auf 9,3 °C (1991–2020); die Niederschläge verteilen sich recht gleichmäßig über das Jahr mit einem leichten Sommermaximum.</t>
   </si>
   <si>
@@ -230,15 +206,9 @@
     <t>Comparatively high livestock density. High proportion of grassland. High proportion of forest. Relatively small farm sizes and field sizes</t>
   </si>
   <si>
-    <t>Exposed to the prevailing wind direction, slope rainfall, lower temperatures compared to the plains.</t>
-  </si>
-  <si>
     <t>Peripheral areas – long distances to regional centres. Population structure: decline, ageing. Comparatively low disposable household income.</t>
   </si>
   <si>
-    <t>Low mountain regions 400-1000 m altitude with high relief energy.</t>
-  </si>
-  <si>
     <t>Soil types are highly variable: Podzolic brown soils with low base saturation, red sandstone, brown soils with high to medium base saturation, pseudogley, parabraun soils from loess with high base saturation, rendzina on calcareous sites (locally limited).</t>
   </si>
   <si>
@@ -248,21 +218,12 @@
     <t>Sales market for products (milk, meat, etc.) located far away, lower direct marketing opportunities, Long distances to slaughterhouses and processing companies. Shortage of workers due to migration and ageing population.</t>
   </si>
   <si>
-    <t>Soil erosion during heavy rainfall</t>
-  </si>
-  <si>
     <t>Vergleichsweise hohe Viehbesatzdichte. Hoher Anteil an Grünland. Hoher Waldanteil. Relativ kleine Betriebs- und Feldgrößen.</t>
   </si>
   <si>
-    <t>Der vorherrschenden Windrichtung ausgesetzt, Hangniederschläge, niedrigere Temperaturen im Vergleich zur Ebene.</t>
-  </si>
-  <si>
     <t>Randgebiete – große Entfernungen zu regionalen Zentren. Bevölkerungsstruktur: Rückgang, Überalterung. Vergleichsweise geringes verfügbares Haushaltseinkommen.</t>
   </si>
   <si>
-    <t>Niedriggebirgsregionen in 400–1000 m Höhe mit hoher Reliefenergie.</t>
-  </si>
-  <si>
     <t>Die Bodenarten sind sehr unterschiedlich: podzolische Braunböden mit geringer Basensättigung, roter Sandstein, Braunböden mit hoher bis mittlerer Basensättigung, Pseudogley, Parabraunböden aus Löss mit hoher Basensättigung, Rendzina auf kalkhaltigen Standorten (lokal begrenzt).</t>
   </si>
   <si>
@@ -272,57 +233,18 @@
     <t>Die Absatzmärkte für Produkte (Milch, Fleisch usw.) liegen weit entfernt, es gibt weniger Möglichkeiten für den Direktvertrieb, und die Entfernungen zu Schlachthöfen und Verarbeitungsbetrieben sind groß. Es herrscht Arbeitskräftemangel aufgrund von Abwanderung und einer alternden Bevölkerung.</t>
   </si>
   <si>
-    <t>Bodenerosion bei starken Regenfällen.</t>
-  </si>
-  <si>
     <t>Rheingau / Rheingau</t>
   </si>
   <si>
     <t>Manager: Kristina Heilemann &lt;Kristina.Heilemann@zalf.de&gt;   |   Slug: rheingau</t>
   </si>
   <si>
-    <t>Soils change over very short distances. Deep, fertile loess and loess loam cover the gentler lower slopes and the plain near the Rhine, Taunus quartzite dominates the higher sites of the central and eastern Rheingau and the Lorch area, and phyllite and Hunsrück slate carry the vineyards of Rüdesheim, Assmannshausen, Kiedrich, Martinsthal and Rauenthal. Beneath the loess cover, weakly leached loess typically overlies deeply weathered phyllite saprolite. The stony slope soils are shallow with low water storage capacity, while the loess soils of the plain are among the most productive arable soils in the region.</t>
-  </si>
-  <si>
-    <t>German wine is in a structural market crisis: bulk wine prices have fallen below production costs, domestic demand for alcoholic drinks keeps declining, and trade barriers make exports harder. Steep-slope viticulture is highly labour-intensive and qualified seasonal workers are scarce, so rising wages, energy costs and regulatory burden bite hardest exactly where the landscape value is greatest. Late frost, hail, heavy rain and drought increase the risk of every vintage, and the dense clusters of Riesling remain vulnerable to fungal disease and pests. Small, fragmented holdings limit mechanisation and make succession increasingly uncertain.</t>
-  </si>
-  <si>
-    <t>Warming is pushing Riesling towards its comfort limit: earlier budburst and ripening, higher sugar and alcohol levels and falling acidity threaten the filigree style the region is known for. Earlier budburst also raises exposure to late frost, while more hot days bring sunburn on the grapes. The climate is shifting towards an alternation of longer dry spells and heavy rainfall, so the climatic water balance deteriorates in summer and irrigation demand grows on the shallow slope soils.</t>
-  </si>
-  <si>
-    <t>Whole villages depend economically, socially and culturally on wine: if estates disappear, the result is not only scrubbed-over slopes but empty villages, closed wine taverns and a weakened tourism offer. Falling wine prices and rising costs squeeze margins, and businesses compete for skilled labour with the far larger Rhine-Main job market, which also drives up land and housing costs. Tourism is strongly seasonal and weather-dependent, and the peripheral communities in the Taunus and the Wisper valleys are much further from centres and services than the settlements along the Rhine axis.</t>
-  </si>
-  <si>
     <t>Steep slopes and terraces can only be worked with high manual effort; where cultivation is abandoned, scrub encroachment erases both the terraced cultural landscape and the dry, warm habitats it carries. Heritage and scenic protection set narrow limits for new infrastructure, while land is simultaneously sought for renewable energy and settlement growth. Small, fragmented parcels make land consolidation difficult, and drought stress is increasingly visible in the forests.</t>
   </si>
   <si>
     <t>Heavy rainfall causes soil erosion on the steep slopes, particularly where rows run downslope and the ground is kept bare. Warmer soils mineralise organic matter faster, so humus is lost just where it matters most for water retention and nutrient supply. Machinery traffic compacts the soil, and nutrient leaching into groundwater remains a concern in the permanent-crop areas.</t>
   </si>
   <si>
-    <t>Der Weinbau prägt die Region: Rund 2.700 ha Rebfläche machen 14 % der landwirtschaftlichen Nutzfläche des Kreises aus, davon etwa 85 % Riesling und 11 % Spätburgunder, bewirtschaftet von rund 280 Haupterwerbswinzern – überwiegend kleine Familienbetriebe neben historischen Einrichtungen wie Kloster Eberbach. Ackerland nimmt 55 % und Dauergrünland 31 % der rund 19.700 ha ein, die von etwa 620 Betrieben bewirtschaftet werden. Außerhalb der Weinberge sind Getreidebau, Schweinemast und Pensionspferdehaltung die wichtigsten Betriebszweige; rund 13 % der Betriebe wirtschaften ökologisch.</t>
-  </si>
-  <si>
-    <t>Nach Norden durch den Taunuskamm vor kühlen Winden geschützt und vom Rhein begünstigt, der Wärme speichert und Licht auf die südexponierten Hänge reflektiert, zählt der Rheingau zu den mildesten Regionen Deutschlands: Die Jahresmitteltemperatur liegt bei rund 10,5 °C; milde Winter, warme Sommer und Herbstnebel begünstigen eine späte Traubenreife. Mit etwa 500–550 mm Jahresniederschlag ist die Region für deutsche Verhältnisse niederschlagsarm. Die Jahresmitteltemperatur in Hessen stieg von 8,2 °C (1961–1990) auf 9,3 °C (1991–2020); das Rhein-Main-Gebiet gehört zu den wärmsten Landesteilen.</t>
-  </si>
-  <si>
-    <t>Im Kreis leben rund 185.700 Menschen bei einer Bevölkerungsdichte von 113 Einwohnern je km², am nordwestlichen Rand der Metropolregion Frankfurt/Rhein-Main. Die Wirtschaft ist mittelständisch geprägt, mit High-Tech-Betrieben in der Informations- und Kommunikationstechnik, Sensorik, Mess- und Regeltechnik sowie Medizin-, Oberflächen- und Umwelttechnik; rund 46.000 sozialversicherungspflichtig Beschäftigte am Arbeitsort und etwa 8.000 Unternehmen stehen einem Auspendlerüberschuss gegenüber, vor allem in Richtung Wiesbaden, Mainz und Frankfurt. Wein und Tourismus sind die prägenden Branchen: rund 240.000 Gästeankünfte und 701.000 Übernachtungen (2021) sowie starke Tagesgästeströme, angezogen von Riesling, Rheinromantik und Veranstaltungen wie dem Rheingau Musik Festival.</t>
-  </si>
-  <si>
-    <t>Ein west-östlich verlaufendes Band zwischen Rhein und Taunus mit südexponierten Hängen und Flussterrassen, auf denen Steillagen- und Terrassenweinbau unterhalb des bewaldeten Rheingaugebirges liegt. Der Waldanteil beträgt rund 56 % der Kreisfläche – deutlich über dem hessischen Durchschnitt –, und der etwa 21.000 ha große Hinterlandswald ist das größte zusammenhängende Waldgebiet Hessens. Der untere Rheingau von Rüdesheim bis Lorchhausen gehört zum UNESCO-Welterbe „Oberes Mittelrheintal“; mit dem Limes liegt ein zweites Welterbe im Kreis. Der Naturpark Rhein-Taunus, die Täler von Wisper, Aar und Wörsbach, Klöster wie Eberbach und historische Weinorte ergänzen eine vielschichtige Kulturlandschaft.</t>
-  </si>
-  <si>
-    <t>Die Böden wechseln auf kurzer Distanz. Tiefgründiger, fruchtbarer Löss und Lösslehm bedecken die flacheren Unterhänge und die Ebene am Rhein, Taunusquarzit prägt die höheren Lagen des mittleren und östlichen Rheingaus sowie den Raum Lorch, und Phyllit und Hunsrückschiefer tragen die Weinberge von Rüdesheim, Assmannshausen, Kiedrich, Martinsthal und Rauenthal. Unter der Lössdecke liegt meist schwach entkalkter Löss über tiefgründig verwittertem Phyllit-Saprolith. Die steinigen Hangböden sind flachgründig und speichern wenig Wasser, während die Lössböden der Ebene zu den ertragreichsten Ackerböden der Region zählen.</t>
-  </si>
-  <si>
-    <t>Der deutsche Weinbau steckt in einer strukturellen Absatzkrise: Die Fassweinpreise liegen unter den Produktionskosten, die Nachfrage nach alkoholischen Getränken geht seit Jahren zurück, und Handelshemmnisse erschweren den Export. Der Steillagenweinbau ist sehr arbeitsintensiv und qualifizierte Saisonkräfte sind schwer zu finden, sodass steigende Löhne, Energiekosten und bürokratische Auflagen dort am stärksten wirken, wo der Landschaftswert am größten ist. Spätfrost, Hagel, Starkregen und Trockenheit erhöhen das Risiko jedes Jahrgangs, und die dichten Trauben des Rieslings bleiben anfällig für Pilzkrankheiten und Schädlinge. Kleine, stark parzellierte Betriebe erschweren Mechanisierung und Hofnachfolge.</t>
-  </si>
-  <si>
-    <t>Die Erwärmung bringt den Riesling an seine Komfortgrenze: früherer Austrieb und frühere Reife, höhere Zucker- und Alkoholgehalte sowie sinkende Säure gefährden den filigranen Stil, für den die Region bekannt ist. Der frühere Austrieb erhöht zugleich das Spätfrostrisiko, und mehr heiße Tage führen zu Sonnenbrand an den Trauben. Das Klima verschiebt sich hin zu einem Wechsel aus längeren Trockenperioden und Starkregen, sodass sich die klimatische Wasserbilanz im Sommer verschlechtert und der Bewässerungsbedarf auf den flachgründigen Hangböden steigt.</t>
-  </si>
-  <si>
-    <t>Ganze Ortschaften hängen wirtschaftlich, sozial und kulturell am Wein: Verschwinden die Betriebe, bleiben nicht nur verbuschte Hänge, sondern auch leere Dörfer, geschlossene Straußwirtschaften und ein geschwächtes touristisches Angebot. Sinkende Weinpreise und steigende Kosten drücken die Margen, und die Betriebe konkurrieren mit dem weit größeren Arbeitsmarkt Rhein-Main um Fachkräfte, was zugleich Boden- und Wohnkosten treibt. Der Tourismus ist stark saison- und witterungsabhängig, und die peripheren Gemeinden im Taunus und in den Wispertälern liegen deutlich weiter von Zentren und Versorgungseinrichtungen entfernt als die Orte entlang der Rheinachse.</t>
-  </si>
-  <si>
     <t>Steillagen und Terrassen lassen sich nur mit hohem Handarbeitsaufwand bewirtschaften; wird die Nutzung aufgegeben, gehen mit der Verbuschung sowohl die Terrassenkulturlandschaft als auch ihre trockenwarmen Lebensräume verloren. Denkmal- und Landschaftsschutz setzen neuer Infrastruktur enge Grenzen, während zugleich Flächen für erneuerbare Energien und Siedlungsentwicklung nachgefragt werden. Die kleinteilige Parzellierung erschwert die Flurneuordnung, und in den Wäldern zeigt sich zunehmender Trockenstress.</t>
   </si>
   <si>
@@ -335,21 +257,6 @@
     <t>DE — Overview</t>
   </si>
   <si>
-    <t>Viticulture defines the region: around 2,700 ha of vines make up 14% of the district's agricultural area, roughly 85% Riesling and 11% Pinot Noir, worked by some 280 full-time growers — mostly small family estates alongside historic institutions such as Kloster Eberbach. Arable land accounts for 55% and permanent grassland for 31% of the roughly 19,700 ha farmed by Overview 620 holdings. Outside the vineyards the main branches are cereal-based arable farming, pig fattening and livery horse keeping; around 13% of farms are managed organically.</t>
-  </si>
-  <si>
-    <t>Sheltered from northerly winds by the Taunus ridge and favoured by the Rhine, which stores heat and reflects light onto the south-facing slopes, the Rheingau is one of the mildest parts of Germany: an annual mean of Overview 10.5 °C, mild winters, warm summers and autumn mists that favour late ripening. With roughly 500–550 mm of annual precipitation it is dry by German standards. Hesse's annual mean temperature rose from 8.2 °C (1961–1990) to 9.3 °C (1991–2020), and the Rhine-Main area is among the warmest parts of the state.</t>
-  </si>
-  <si>
-    <t>Overview 185,700 people live in the district at 113 inhabitants per km², on the north-western edge of the Frankfurt/Rhine-Main metropolitan region. The economy is dominated by small and medium-sized firms, including high-tech in information and communication technology, sensor and control engineering, medical, surface and environmental technology; some 46,000 jobs and 8,000 registered businesses stand against a net outflow of commuters, mainly towards Wiesbaden, Mainz and Frankfurt. Wine and tourism are the signature sectors: around 240,000 arrivals and 701,000 overnight stays (2021) plus strong day-visitor flows, drawn by Riesling, Rhine romanticism and events such as the Rheingau Musik Festival.</t>
-  </si>
-  <si>
-    <t>An east–west band between the Rhine and the Taunus, with south-facing slopes and river terraces carrying steep-slope and terraced vineyards below the wooded Rheingaugebirge. Forest covers Overview 56% of the district — well above the Hessian average — and the roughly 21,000 ha Hinterlandswald is the largest contiguous forest area in Hesse. The lower Rheingau from Rüdesheim to Lorchhausen belongs to the UNESCO World Heritage site 'Upper Middle Rhine Valley', with the Limes as a second World Heritage site in the district. The Rhein-Taunus Nature Park, the Wisper, Aar and Wörsbach valleys, monasteries such as Kloster Eberbach and historic wine villages complete a densely layered cultural landscape.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUT3 code: </t>
-  </si>
-  <si>
     <t>Exemplar research projects</t>
   </si>
   <si>
@@ -362,26 +269,333 @@
     <t>Location data</t>
   </si>
   <si>
-    <t>Short description</t>
-  </si>
-  <si>
-    <t>URL/link</t>
-  </si>
-  <si>
-    <t>Consent to include</t>
-  </si>
-  <si>
     <t>Practice partners</t>
   </si>
   <si>
     <t>Enter one practice partner per row. Please provide 2–3 examples.</t>
+  </si>
+  <si>
+    <t>Location data (Google maps entry or coordinates)</t>
+  </si>
+  <si>
+    <t>Short description (overview of activities or their research interests)</t>
+  </si>
+  <si>
+    <t>Short description (overview of project topic/goals)</t>
+  </si>
+  <si>
+    <t>URL/link (can be to ZALF website page)</t>
+  </si>
+  <si>
+    <t>URL/link (Website)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Rheingau ist vom Weinbau geprägt, bekannt für die weiße Sorte Riesling sowie Spätburgunder bei den roten Sorten. Zum großen Teil sind es kleine Familienbetriebe,  die die Weinberge bewirtschaften, neben historischen Einrichtungen wie Kloster Eberbach.  </t>
+  </si>
+  <si>
+    <t>Der (deutsche) Weinbau steckt in einer strukturellen Absatzkrise: Die Fassweinpreise liegen unter den Produktionskosten, die Nachfrage nach alkoholischen Getränken geht seit Jahren zurück, und Handelshemmnisse erschweren den Export. Der Steillagenweinbau ist sehr arbeitsintensiv und qualifizierte Saisonkräfte sind schwer zu finden, sodass steigende Löhne, Energiekosten und bürokratische Auflagen dort am stärksten wirken, wo der Landschaftswert am größten ist. Kleine, stark parzellierte Betriebe erschweren Mechanisierung und Hofnachfolge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nach Norden durch den Taunuskamm vor kühlen Winden geschützt und vom Rhein begünstigt, der Wärme speichert und Licht auf die südexponierten Hänge reflektiert. Der Rheingau zählt zu den mildesten und niederschlagsärmsten Regionen Deutschlands. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Erwärmung bringt einen früheren Austrieb und frühere Reife, höhere Zucker- und Alkoholgehalte sowie sinkende Säure gefährden den filigranen Stil, für den die Region bekannt ist. Der frühere Austrieb erhöht zugleich das Spätfrostrisiko, und mehr heiße Tage führen zu Sonnenbrand an den Trauben. Die Zunahme von Niederschlags Extremen (Dürre und Starkregen) führt in einem Jahr zu Trockenstress und im anderen Jahr zu hohem Pilzdruck. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganze Ortschaften hängen wirtschaftlich, sozial und kulturell am Wein: Verschwinden die Betriebe, bleiben nicht nur verbuschte Hänge, sondern auch leere Dörfer, geschlossene Straußwirtschaften und ein geschwächtes touristisches Angebot. Sinkende Weinpreise und steigende Kosten drücken die Margen, und die Betriebe konkurrieren mit dem weit größeren Arbeitsmarkt Rhein-Main um Fachkräfte, was zugleich Boden- und Wohnkosten treibt. </t>
+  </si>
+  <si>
+    <t>Ein west-östlich verlaufendes Band zwischen Rhein und Taunus mit südexponierten Hängen und Flussterrassen, auf denen Steillagen- und Terrassenweinbau unterhalb des bewaldeten Rheingaugebirges liegt. Der Waldanteil liegt  deutlich über dem hessischen Durchschnitt. Der untere Rheingau von Rüdesheim bis Lorchhausen gehört zum UNESCO-Welterbe „Oberes Mittelrheintal“; mit dem Limes liegt ein zweites Welterbe im Kreis. Der Naturpark Rhein-Taunus, die Täler von Wisper, Aar und Wörsbach, Klöster wie Eberbach und historische Weinorte ergänzen eine vielschichtige Kulturlandschaft.</t>
+  </si>
+  <si>
+    <t>Die Böden wechseln auf kurzer Distanz. Tiefgründiger, fruchtbarer Löss und Lösslehm bedecken die flacheren Unterhänge und die Ebene am Rhein, Taunusquarzit prägt die höheren Lagen des mittleren und östlichen Rheingaus sowie den Raum Lorch, und Phyllit und Hunsrückschiefer tragen die Weinberge von Rüdesheim, Assmannshausen, Kiedrich, Martinsthal und Rauenthal. Die steinigen Hangböden sind flachgründig und speichern wenig Wasser, während die Lössböden der Ebene zu den ertragreichsten Ackerböden der Region zählen.</t>
+  </si>
+  <si>
+    <t>(German) wine is in a structural market crisis: bulk wine prices have fallen below production costs, domestic demand for alcoholic drinks keeps declining, and trade barriers make exports harder. Steep-slope viticulture is highly labour-intensive and qualified seasonal workers are scarce, so rising wages, energy costs and regulatory burden bite hardest exactly where the landscape value is greatest. Small, fragmented holdings limit mechanisation and make succession increasingly uncertain.</t>
+  </si>
+  <si>
+    <t>Warming leads to an earlier budburst and ripening, higher sugar and alcohol levels and falling acidity threaten the filigree style the region is known for. Earlier budburst also raises exposure to late frost, while more hot days bring sunburn on the grapes. The increase of precipitation extremes (Drought and heavy rain) is leading in one year to drought stress and in the other to high disease pressure by fungi.</t>
+  </si>
+  <si>
+    <t>Sheltered from northerly winds by the Taunus ridge and favoured by the Rhine, which stores heat and reflects light onto the south-facing slopes. The Rheingau is one of the mildest parts of Germany with low precipitation.</t>
+  </si>
+  <si>
+    <t>North Hessian / Nordhessen</t>
+  </si>
+  <si>
+    <t>Manager: Silke Flörke &lt;Silke.Floerke@zalf.de&gt;   |   Slug: north-hessian</t>
+  </si>
+  <si>
+    <t>Die Landwirtschaft ist kleinstrukturiert und getreidebetont: Winterweizen, Wintergerste und Winterraps bilden das Grundgerüst der Fruchtfolge, Getreide steht auf rund zwei Dritteln der Ackerfläche, daneben Feldfutterbau, Ölfrüchte und ein wachsendes Spektrum an Nischenkulturen – beim Hanfanbau ist der Werra-Meißner-Kreis hessenweit führend. Der Ökolandbau ist ungewöhnlich stark und hat sich zwischen 2009 und 2019 nahezu verdoppelt: Im Werra-Meißner-Kreis wirtschaften 12 % der Betriebe auf 14,4 % der landwirtschaftlichen Nutzfläche ökologisch, deutlich über dem Bundeswert; getragen wird dies vom Fachbereich Ökologische Agrarwissenschaften der Universität Kassel in Witzenhausen – dem weltweit ersten seiner Art –, der Hessischen Staatsdomäne Frankenhausen, dem Lehr-und Versuchsbetrieb für ökologische Landwirtschaft und Nachhaltige Regionalentwicklung und der Ökolandbau-Modellregion Nordhessen. Die Nutztierdichte ist vergleichsweise gering und rückläufig: Die Milchviehhaltung geht stark zurück, während Mutterkühe, Schafe, Pferde und Geflügel zulegen. Rund ein Drittel der Ackerflächen und über die Hälfte des Grünlands werden über Agrarumweltmaßnahmen oder ökologisch bewirtschaftet.</t>
+  </si>
+  <si>
+    <t>The economy is dominated by small and medium-sized firms, including high-tech in information and communication technology, sensor and control engineering, medical, surface and environmental technology.  Commuters, mainly towards Wiesbaden, Mainz and Frankfurt. Wine and tourism are the signature sectors, strong day-visitor flows, drawn by Riesling, Rhine romanticism and events such as the Rheingau Musik Festival.</t>
+  </si>
+  <si>
+    <t>Whole villages depend economically, socially and culturally on wine: if estates disappear, the result is not only scrubbed-over slopes but empty villages, closed wine taverns and a weakened tourism offer. Falling wine prices and rising costs squeeze margins, and businesses compete for skilled labour with the far larger Rhine-Main job market, which also drives up land and housing costs.</t>
+  </si>
+  <si>
+    <t>An east–west band between the Rhine and the Taunus, with south-facing slopes and river terraces carrying steep-slope and terraced vineyards below the wooded Rheingaugebirge. Forest cover is well above the Hessian average The lower Rheingau from Rüdesheim to Lorchhausen belongs to the UNESCO World Heritage site 'Upper Middle Rhine Valley', with the Limes as a second World Heritage site in the district. The Rhein-Taunus Nature Park, the Wisper, Aar and Wörsbach valleys, monasteries such as Kloster Eberbach and historic wine villages complete a densely layered cultural landscape.</t>
+  </si>
+  <si>
+    <t>Soils change over very short distances. Deep, fertile loess and loess loam cover the gentler lower slopes and the plain near the Rhine, Taunus quartzite dominates the higher sites of the central and eastern Rheingau and the Lorch area, and phyllite and Hunsrück slate carry the vineyards of Rüdesheim, Assmannshausen, Kiedrich, Martinsthal and Rauenthal.  The stony slope soils are shallow with low water storage capacity, while the loess soils of the plain are among the most productive arable soils in the region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Rheingau region is defined by viticulture and is known for the white grape variety Riesling as well as Pinot noir among the red varieties. For the most part, it is small family-run businesses that cultivate the vineyards, alongside historic institutions such as Eberbach Abbey.  </t>
+  </si>
+  <si>
+    <t>Die Wirtschaft ist mittelständisch geprägt, mit High-Tech-Betrieben in der Informations- und Kommunikationstechnik, Sensorik, Mess- und Regeltechnik sowie Medizin-, Oberflächen- und Umwelttechnik. Pendler vor allem in Richtung Wiesbaden, Mainz und Frankfurt. Wein und Tourismus sind die prägenden Branchen, es gibt starke Tagesgästeströme im Sommer, angezogen von Riesling, Rheinromantik und Veranstaltungen wie dem Rheingau Musik Festival.</t>
+  </si>
+  <si>
+    <t>GeisTreich</t>
+  </si>
+  <si>
+    <t>https://geistreich.hs-geisenheim.de/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer program for a biodiverse and multifunctional viticulture. Link university´s research findings with the experience of stakeholders to develop innovative ideas together for a sustainable viticulture. </t>
+  </si>
+  <si>
+    <t>KliA-Net</t>
+  </si>
+  <si>
+    <t>AmBiTo</t>
+  </si>
+  <si>
+    <t>https://www.eltville.de/leben-wohnen/nachhaltiges-eltville/klimaschutz-anpassungen/klia-net/</t>
+  </si>
+  <si>
+    <t>Develeoping strategies that will enable the Rheingau region to respond to climate change. The network consists of all relevant sectors in the region</t>
+  </si>
+  <si>
+    <t>https://www.ambito.eco/</t>
+  </si>
+  <si>
+    <t>Biodiversity measures tailored to specific regions and individual needs are developed, tested and implement in strong collaboration with the winemakers.</t>
+  </si>
+  <si>
+    <t>Bei Ausrichtung der Mittelgebirge zur Hauptwindrichtung sind stark ausgeprägte Steigungsregen - im Windschatten der Gebirge geringere Niederschläge zu erwarten. Es herschen niedrigere Temperaturen im Vergleich zur Ebene vor. Die Schneebedeckung im Winter ist höher und dauert länger an als in den Niederungen.</t>
+  </si>
+  <si>
+    <t>Where low mountain ranges are aligned with the prevailing wind direction, heavy orographic rainfall is to be expected, whilst precipitation is lower in the lee of the mountains. Temperatures are lower here than on the plains. Snow cover in winter is deeper and lasts longer than in the lowlands.</t>
+  </si>
+  <si>
+    <t>Auch in den Mittelgebirgen werden häufiger Starkregenereignissen und eine höhere Anzahl von Hitzetagen verzeichnet. Dies kann sich schädlich auf die Futterproduktion auswirken.</t>
+  </si>
+  <si>
+    <t>In the low mountain ranges, heavy rainfall events are becoming more frequent and there are a greater number of hot days. This can have a detrimental effect on forage production.</t>
+  </si>
+  <si>
+    <t>Mittelgebirgsregionen in 400–1000 m Höhe mit hoher Reliefenergie. Strukturreiche Landschaft durch Hecken und Säume. Kleinteiliger Wechsel von Grünland und Äckern. Die Beibehaltung der Grünlandwirtschaft ist abhängig von der Anzahl der viehhaltenden Betrieben.</t>
+  </si>
+  <si>
+    <t>Low mountain regions 400-1000 m altitude with high relief energy. The agricultural landscape is characterised by hedgerows and field margins and a patchwork of grassland and arable fields. The continuation of grassland farming depends on the maintanance of cattle farms.</t>
+  </si>
+  <si>
+    <t>Periphere Räume sind einem hohen Druck durch die Errichtung von Windenergie- und Photovoltaikanlagen ausgesetzt. Große Flächenanteile sind durch Naturschutzrechtliche Auflagen (z.B. Natura 2000) in der Nutzung eingeschränkt. Der Rückgang von Haupt- und v.a. Nebenerwerbslandwirten wird eine Änderung des Landschaftsbildes hin zu einheitlicheren Strukturen zur Folge haben.</t>
+  </si>
+  <si>
+    <t>Peripheral areas are under considerable pressure due to the construction of wind farms and solar power plants. The use of large areas of land is restricted by nature conservation legislation (e.g. Natura 2000). The decline in the number of full-time and, in particular, part-time farmers will result in a change to the landscape, leading to more uniform structures.</t>
+  </si>
+  <si>
+    <t>Aufgrund der zunehmenden Verdunstung verschlechtert sich der klimatische Wasserhaushalt im betrachteten Gebiet insgesamt. Dies macht sich insbesondere im Sommer bemerkbar und ist eine Entwicklung, die in Zukunft zunehmend an Bedeutung gewinnen wird. Die Jahresniederschläge verteilen sich auch im Havelland immer stärker auf Starkregenereignisse, die von immer längeren Dürreperioden unterbrochen werden.</t>
+  </si>
+  <si>
+    <t>Due to increasing evaporation, the climatic water balance in the area under consideration is generally deteriorating. This is particularly evident in summer and is a development that will become increasingly significant in the future. In the Havelland region, too, annual precipitation is increasingly concentrated in heavy rain events, which are interrupted by ever-longer periods of drought.</t>
+  </si>
+  <si>
+    <t>Havelland</t>
+  </si>
+  <si>
+    <t>Havelland gehört zur norddeutschen Tiefebene und verfügt über sandige Schwemmlandböden. Die Qualität der Ackerböden nimmt von Westen nach Osten zu. Das Havelland verfügt noch über ca. 28.000ha an Moorböden. Die Nitratbelastung der Böden ist im deutschlandweiten Vergleich eher gering.</t>
+  </si>
+  <si>
+    <t>Havelland is classified as part of the North German inland lowlands and has sandy, diluvial soils. The quality of the arable soil increases from west to east. The Havelland region still has approximately 28,000 hectares of peatland. Compared to the rest of Germany, nitrate contamination of the soil is relatively low.</t>
+  </si>
+  <si>
+    <t>As in other German regions, the soils of the agricultural areas in the Havelland are also affected by degradation. In many places, the peat soils have been irreversibly degraded as a result of decades of landscape drainage.</t>
+  </si>
+  <si>
+    <t>Die Böden der Ackerbaustandorte im Havelland sind wie in anderen deutschen Region auch von Degradation betroffen. Die Moorböden wurden durch die jahrzehntelange Entwässerung der Landschaften vielerorts irreversibel abgebaut.</t>
+  </si>
+  <si>
+    <t>Agriculture in the Havelland region is undergoing structural change. The region’s traditional extensive grassland farming, with its livestock herds, is in a phase of decline. New, lucrative business models for managing wet meadows are being sought. Successors are urgently needed for the farm operations—some of which are very large—that date back to the GDR era. The market advantages offered by the nearby Berlin metropolitan region for increased regional production and sales are not yet being fully exploited.</t>
+  </si>
+  <si>
+    <t>Ausgedehnte Urstromtalungen bestimmen das Landschaftsbild im Havelland. Inselartig ragen daraus Platten hervor (z.B. die Nauener Platte), die meistens Grundmoränen tragen. Ausgedehnten Wiesen in den Niederungen stehen Acker und Waldbestand auf den Hochgebieten (sog. "Ländchen") gegenüber. Das mosaikartige Nebeneinander von Hochflächen mit Inselcharakter und ausgedehnten Niederungszügen bestimmen den Charakter dieses Naturraumes. Die meist flachwelligen Inseln heben sich deutlich von den sie umgebenden Niederungen ab.</t>
+  </si>
+  <si>
+    <t>Extensive glacial valleys dominate the landscape of the Havelland. Plateaus (such as the Nauener Plateau) rise from these valleys like islands, most of which are topped by ground moraines. Extensive meadows in the lowlands contrast with farmland and forests on the higher elevations (so-called “Ländchen”). The mosaic-like juxtaposition of island-like plateaus and extensive lowland stretches defines the character of this natural region. The mostly gently undulating plateaus stand out clearly from the surrounding lowlands.</t>
+  </si>
+  <si>
+    <t>The farms in the Havelland region—some of which date back to the GDR era—have led to the development of large-scale field units; these tend to go hand in hand with the emergence of monocultures and weaken the resilience of landscapes. From a resilience perspective, greater landscape structuring should be pursued. In many places, the infrastructure for regulating water levels in the landscape is not intact.</t>
+  </si>
+  <si>
+    <t>Die zum Teil aus der DDR-Zeit herrührenden Betriebsformen im Havelland haben zu der Entwicklung zum Teil sehr großer landwirtschaftlicher Schläge geführt, die tendenziell die Ausprägung von Monokulturen begleiten und die Resilienz von Landschaften schwächen. Aus Resilienzperspektive wäre eine stärkere Strukturierung der Landschaft anzustreben. Die Infrastrukturen zur Regulierung der Landschaftswasserstände sind vielerorts nicht intakt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Landwirtschaft im Havelland steckt in einem Strukturwandel. Die traditionelle extensive Grünlandbewirtschaftung der Region mit ihren Viehbeständen, befindet sich in einer Degressionsphase. Neue, lukrative Geschäftsmodelle für die Bewirtschaftung von Feuchtwiesen werden gesucht. Für die zum Teil sehr großen Betriebseinheiten aus DDR-Zeit werden zeitnah Nachfolger gebraucht. Die Marktvorteile der nahen Metropolregion Berlin für mehr regionale Produktion und Absatz werden noch nicht voll ausgeschöpft. </t>
+  </si>
+  <si>
+    <t>NUTS 3 code: DE408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FInAL: Förderung von Insekten in Agrarlandschaften </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 landscape areas in Havelland </t>
+  </si>
+  <si>
+    <t>FinAL develops, demonstrates and evaluates innovative measures for facilitating insects through integrated cultivation of renewable resources in a landscape context</t>
+  </si>
+  <si>
+    <t>https://www.final-projekt.de/en/</t>
+  </si>
+  <si>
+    <t>F.R.A.N.Z.: Future Resources, Agriculture &amp; Nature Conservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havelland </t>
+  </si>
+  <si>
+    <t>FRANZ is a dialogue and demonstration project in which effective nature protection measures have been developed and that can be integrated into normal farming practice.</t>
+  </si>
+  <si>
+    <t>https://www.franz-projekt.de/franz</t>
+  </si>
+  <si>
+    <t>ZirKUH</t>
+  </si>
+  <si>
+    <t>KlimaTier</t>
+  </si>
+  <si>
+    <t>https://www.uni-giessen.de/de/fbz/fb09/forschung/lehreinrichtungen/Standorte_neu/gh</t>
+  </si>
+  <si>
+    <t>Gladbacher Hof</t>
+  </si>
+  <si>
+    <t>The teaching and research unit Gladbacherhof at the Villmar site primarily serves research and teaching in the field of organic farming</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RzCPHEKwFwChuDwt5</t>
+  </si>
+  <si>
+    <t>https://www.uni-giessen.de/en/faculties/f09/institutes/landscape/water/research/active/zirkuh</t>
+  </si>
+  <si>
+    <t>Circular cattle farming systems in Hesse to strengthen regional value chains for dairy and beef</t>
+  </si>
+  <si>
+    <t>https://www.uni-giessen.de/de/fbz/fb09/institute/ibae/bea/projekte/klimatier</t>
+  </si>
+  <si>
+    <t>Klimaschutz durch Tierhaltung</t>
+  </si>
+  <si>
+    <t>Bodenerosion bei Starkregenereignissen. Lokal flachgründige, nicht ackerfähige Böden.</t>
+  </si>
+  <si>
+    <t>Soil erosion during heavy rainfall, locally shallow non arable soils</t>
+  </si>
+  <si>
+    <t>East Brandenburg / Ostbrandenburg</t>
+  </si>
+  <si>
+    <t>NUT3 code: DE409 (Landkreis Märkisch-Oderland) und DE40C (Landkreis Oder-Spree)</t>
+  </si>
+  <si>
+    <t>Predominantly sandy and loamy-sandy soils with low to moderate natural fertility and limited water-holding capacity. Strong spatial heterogeneity due to the glacial landscape, with more fertile soils in selected areas such as the Oderbruch. Generally low soil quality, with Müncheberger soil ratings often below 50 points.</t>
+  </si>
+  <si>
+    <t>⚠ NEEDS INPUT
+Low water-holding capacity amplifies drought impacts on agricultural productivity. Low natural fertility and nutrient retention capacity increase the need for careful soil and nutrient management. Sandy soils are vulnerable to wind erosion, while heavy rainfall can increase water erosion and soil loss. Maintaining soil organic matter and humus is important for fertility, water retention and climate resilience. Soil compaction and degradation can further reduce soil functions, particularly under intensive cultivation and extreme weather conditions.</t>
+  </si>
+  <si>
+    <t>Überwiegend sandige und lehmig-sandige Böden mit geringer bis mittlerer natürlicher Fruchtbarkeit und begrenzter Wasserspeicherfähigkeit. Aufgrund der glazial geprägten Landschaft besteht eine starke räumliche Heterogenität der Bodenverhältnisse, wobei beispielsweise im Oderbruch fruchtbarere Böden vorkommen. Insgesamt ist die Bodenqualität eher gering; die Müncheberger Bodenbewertung liegt häufig unter 50 Punkten.</t>
+  </si>
+  <si>
+    <t>⚠ NEEDS INPUT
+Die geringe Wasserspeicherfähigkeit verstärkt die Auswirkungen von Trockenheit auf die landwirtschaftliche Produktivität. Die geringe natürliche Fruchtbarkeit und Nährstoffhaltefähigkeit erhöhen den Bedarf an einem sorgfältigen Boden- und Nährstoffmanagement. Sandige Böden sind besonders anfällig für Winderosion, während Starkniederschläge die Gefahr von Wassererosion und Bodenverlust erhöhen können. Der Erhalt der organischen Bodensubstanz und des Humus ist wichtig für Bodenfruchtbarkeit, Wasserspeicherfähigkeit und Klimarobustheit. Bodenverdichtung und Bodendegradation können die Bodenfunktionen zusätzlich beeinträchtigen, insbesondere bei intensiver Bewirtschaftung und unter zunehmenden Extremwetterbedingungen.</t>
+  </si>
+  <si>
+    <t>Increasing temperatures and more frequent heat extremes. Longer and more frequent periods of drought, particularly in spring and summer, combined with increasing variability in precipitation. More frequent extreme weather events, including heavy rainfall, storms and hail, increase uncertainty for land use and agricultural production. Overall, declining water availability and increasing climate variability create growing pressure on regional land and water management.</t>
+  </si>
+  <si>
+    <t>Steigende Temperaturen und häufigere Hitzeextreme. Längere und häufiger auftretende Trockenperioden, insbesondere im Frühjahr und Sommer, gehen mit einer zunehmenden Variabilität der Niederschläge einher. Häufigere Extremwetterereignisse, darunter Starkregen, Stürme und Hagel, erhöhen die Unsicherheit für die Landnutzung und die landwirtschaftliche Produktion. Insgesamt führen die abnehmende Wasserverfügbarkeit und die zunehmende Klimavariabilität zu einem wachsenden Druck auf das regionale Land- und Wassermanagement.</t>
+  </si>
+  <si>
+    <t>LAG Märkische Seen</t>
+  </si>
+  <si>
+    <t>Die Einrichtung einer lokalen Partnerschaft, der sogenannten „Lokalen Aktionsgruppe“ (LAG), ist ein zentrales und charakteristisches Merkmal des LEADER-Ansatzes. Die LAG bringt öffentliche und private Akteure aus unterschiedlichen sozioökonomischen Bereichen der Region zusammen und bildet ein breites Spektrum lokaler Interessen ab. Sie entwickelt und setzt eine lokale Entwicklungsstrategie um, entscheidet über die Verwendung der ihr zur Verfügung stehenden Fördermittel und begleitet deren Umsetzung. Als regional verankertes Netzwerk verbindet die LAG unterschiedliche Akteure, Interessen und Kompetenzen und schafft damit eine wichtige Grundlage für die gemeinsame Gestaltung der regionalen Entwicklung.</t>
+  </si>
+  <si>
+    <t>https://www.lag-maerkische-seen.de/</t>
+  </si>
+  <si>
+    <t>LAG Märkische Seen e.V.
+c/o Campus Schloss Trebnitz
+Haus der Demokratie und Inklusion
+Platz der Jugend 4
+15374 Müncheberg OT Trebnitz</t>
+  </si>
+  <si>
+    <t>Amt für Kreisentwicklung und Infrastruktur, Landkreis Oder-Spree</t>
+  </si>
+  <si>
+    <t>Das Amt für Kreisentwicklung und Infrastruktur bündelt zentrale Aufgaben der regionalen Entwicklung im Landkreis Oder-Spree. Zu seinen Tätigkeitsfeldern gehören unter anderem Kreis- und Verkehrsplanung, Wirtschaftsförderung, ländliche Entwicklung, Mobilitätskonzepte und -angebote sowie die Entwicklung und Vermarktung der Region. Damit verfügt das Amt über wichtige Schnittstellen zu Kommunen, Wirtschaft und weiteren regionalen Akteuren und bringt relevante Kompetenzen für die integrierte Entwicklung und Transformation der Region ein.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Breitscheidstraße 7
+Haus B
+15848 Beeskow
+https://maps.app.goo.gl/6Tnjrzs3zQna4eFd8</t>
+  </si>
+  <si>
+    <t>https://www.landkreis-oder-spree.de/Politik-Landkreis/Kreisverwaltung/Ansprechpartner/Amt-f%C3%BCr-Kreisentwicklung-und-Infrastruktur.php?ModID=9&amp;FID=2689.3728.1</t>
+  </si>
+  <si>
+    <t>https://lpv.mittlere-oder.de/</t>
+  </si>
+  <si>
+    <t>Landschaftspflegeverbandes Mittlere Oder e.V. (LPV).</t>
+  </si>
+  <si>
+    <t>Lindenstraße 7, 15230 Frankfurt (Oder)
+https://share.google/1UDztCFxWtapb40jX</t>
+  </si>
+  <si>
+    <t>Der 1996 gegründete Landschaftspflegeverband Mittlere Oder versteht sich als Schnittstelle zwischen Naturschutz, Landwirtschaft und Behörden. Als anerkannter Naturschutzberater für Landwirte und Träger verschiedener Projekte in Brandenburg verfügt der LPV über umfangreiche Erfahrungen in der Verbindung von landwirtschaftlicher Nutzung und Naturschutz. In Kooperation mit Naturparkverwaltungen, Bauernverbänden, Stiftungen und weiteren regionalen sowie polnischen Partnern setzt er sich für den Erhalt der Artenvielfalt und ihrer Lebensräume ein und unterstützt Landwirte bei der Umsetzung naturschutzfachlicher Maßnahmen auf landwirtschaftlichen Flächen.</t>
+  </si>
+  <si>
+    <t>SUNFLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 befanden sich ca. ¼ der deutschen Anbauflächen für Sonnenblumen mit 17.200 ha in Brandenburg, davon die meisten in Ost- und Südbrandenburg. Aktuell verlässt jedoch ein Großteil der Erträge die Region Ostbrandenburg und wird Teil globalisierter Wertschöpfungsketten. Neben positiven Aspekten wie der Effizienzsteigerung der Lebensmittelproduktion führt eine globalisierte Wertschöpfung jedoch auch zu zahlreichen Nachteilen wie bspw. zu einer sinkenden Biodiversität am Lebensmittelproduktionsstandort, einer sinkenden Transparenz über den Herstellungsprozess der Lebensmittel, als auch zu einer ungleichen Verteilung der Wertschöpfung unter den Wertschöpfungsketten-Akteuren. Um diese Nachteile zu überwinden und Agrar- und Ernährungssysteme nachhaltiger zu gestalten kann die Implementierung regionaler Wertschöpfungsnetzwerke sinnvoll sein. 
+Hierfür wird im ersten Schritt ein Überblick zu Produktions- und Verarbeitungsbetrieben und Händlern regionaler Sonnenblumenerzeugnisse für Ostbrandenburg erstellt und anschließend auch ein Überblick zu den Erzeugnissen, Dienstleistungen, Absatzwegen, Potenzialen und Hemmnissen ausgewählter Produzenten. Ein weiteres Ziel des Projekts ist es herauszufinden, welche Produkte sich besonders für eine regionale Verwertung anbieten. Zudem soll die Rolle von Sozialkapital beim Aufbau regionaler Wertschöpfungsketten untersucht werden.
+Die Sonnenblume eignet sich als Beispiel für regionale Wertschöpfung besonders, da sie zahlreiche ökologisch Vorteile mit sich bringt: ein geringer Bedarf an Düngung und Pflanzenschutz, ein biodiversitätsfördernder Charakter und eine passende Vorkultur für Getreide, welches in Brandenburg eine besondere Relevanz hat.
+Praxispartner in diesem Projekt sind: 
+Amt für Kreisentwicklung und Infrastruktur Landkreis Oder-Spree
+Amt für Landwirtschaft und Umwelt Landkreis Märkisch-Oderland
+LAG Märkische Seen e.V.
+In 2025, approximately one-quarter of Germany’s sunflower cultivation area, totaling 17,200 hectares, was located in Brandenburg, primarily in its eastern and southern parts. However, a large share of the harvest leaves Brandenburg to become part of globalized value chains. While globalized value creation offers benefits such as increased efficiency in food production, it also entails numerous drawbacks including reduced biodiversity at production sites, diminished transparency regarding food processing, and an unequal distribution of value among the various actors in the chain. Establishing regional value-creation networks can help to overcome these disadvantages and foster more sustainable food systems.
+As a first step, the project will compile an overview of producers, processors, and traders of regional sunflower products in East Brandenburg, followed by an analysis of their associated products, services, sales channels, opportunities, and obstacles. Another project objective is to identify which products are particularly well-suited for regional utilization. Additionally, the project aims to examine the role of social capital in the development of regional value chains.
+Sunflowers are particularly well-suited for this purpose due to their numerous ecological benefits: low requirements for fertilizers and crop protection agents, a capacity to promote biodiversity, and their suitability as a preceding crop for grain – a crop of significant importance in Brandenburg.
+Project partners are:
+Amt für Kreisentwicklung und Infrastruktur Landkreis Oder-Spree
+Amt für Landwirtschaft und Umwelt Landkreis Märkisch-Oderland
+LAG Märkische Seen e.V.
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,8 +683,54 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,6 +767,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -532,10 +804,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -550,13 +823,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -565,10 +835,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -582,6 +893,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Gunnoltz, Julia" id="{DA0B17B6-5F30-4A90-A859-E7B4E281C91C}" userId="S::julia.gunnoltz@zalf.de::01bd84dc-8e3a-43aa-8452-672629141834" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -867,6 +1184,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B20" dT="2026-08-25T07:01:41.34" personId="{DA0B17B6-5F30-4A90-A859-E7B4E281C91C}" id="{19299B7F-6951-4032-995A-F4A142CB96AA}">
+    <text>google map entry is outdated, tehy recently moved with their office: https://share.google/xhoVIP4xxF6lyL6bZ</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
@@ -890,50 +1215,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -950,179 +1275,203 @@
     </row>
     <row r="5" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
+      <c r="F5" s="26" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>108</v>
+      <c r="A10" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
+      <c r="A11" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>115</v>
+      <c r="A17" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>116</v>
+      <c r="A18" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1130,46 +1479,305 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D20" r:id="rId1" xr:uid="{23F80D9A-0214-41BC-9DE8-CA02A3966961}"/>
+    <hyperlink ref="D21" r:id="rId2" xr:uid="{82951215-3483-4B19-A393-84595EECA33C}"/>
+    <hyperlink ref="D22" r:id="rId3" xr:uid="{CC479ED6-1230-4AC4-A963-E07645F4B248}"/>
+    <hyperlink ref="B22" r:id="rId4" display="https://share.google/1UDztCFxWtapb40jX" xr:uid="{5A09CD35-6E5F-4272-9AAA-3A3FF45A6749}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="6" width="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="250.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -1186,413 +1794,175 @@
     </row>
     <row r="5" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>108</v>
+      <c r="A10" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
+      <c r="A11" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>115</v>
+      <c r="A17" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>116</v>
+      <c r="A18" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="A19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="6" width="48" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1606,38 +1976,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -1654,179 +2024,194 @@
     </row>
     <row r="5" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>56</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>113</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
+        <v>57</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>117</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1840,38 +2225,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -1888,185 +2273,204 @@
     </row>
     <row r="5" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>115</v>
+      <c r="A17" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>116</v>
+      <c r="A18" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="A19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D13" r:id="rId1" xr:uid="{80488B42-5FE6-4B0C-849E-08340AF36C72}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{732F3989-EAD2-4624-BD5E-423EB73DCA2E}"/>
+    <hyperlink ref="D15" r:id="rId3" xr:uid="{8A028371-625F-4FEE-8C4D-E8BEEABE5A2A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>